--- a/docs/DBS6_Campaign_Review_20260928-535a4eef.xlsx
+++ b/docs/DBS6_Campaign_Review_20260928-535a4eef.xlsx
@@ -40136,7 +40136,7 @@
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>OBJECTIVE: tagged Discovery but a Broad campaign is Defensive by the standard | SKU: Broad campaign advertises the White ranking SKU BAMBOO-QUEEN-WHITE-6PCS; it should advertise an LTSF SKU (list pending) | RUN: cuts a campaign that is inside its ceiling (tos 57→51) — hold instead</t>
+          <t>OBJECTIVE: tagged Discovery but a Broad campaign is Defensive by the standard | RUN: cuts a campaign that is inside its ceiling (tos 57→51) — hold instead</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
@@ -40252,12 +40252,12 @@
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>SKU: Broad campaign advertises the White ranking SKU BAMBOO-QUEEN-WHITE-6PCS; it should advertise an LTSF SKU (list pending) | SEARCH TERM: buys 7 exact ranking terms (26 clicks, $76 in 30d) — “bamboo sheets” 13, “bamboo sheets queen size” 5, “viscose bamboo sheets” 3, “bamboo cooling sheets” 2, “bamboo bed sheets” 1</t>
+          <t>SKU: Broad campaign advertises BAMBOO-QUEEN-WHITE-6PCS; the Queen LTSF SKU is BAMBOO-QUEEN-LIGHTOLIVE-6PCS (11 sold in 30 days, 131 Available, 141 days) | SEARCH TERM: buys 7 exact ranking terms (26 clicks, $76 in 30d) — “bamboo sheets” 13, “bamboo sheets queen size” 5, “viscose bamboo sheets” 3, “bamboo cooling sheets” 2, “bamboo bed sheets” 1</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
+          <t>advertise BAMBOO-QUEEN-LIGHTOLIVE-6PCS | negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
         </is>
       </c>
     </row>
@@ -40368,12 +40368,12 @@
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>SKU: Broad campaign advertises the White ranking SKU BAMBOO-KING-WHITE-6PCS; it should advertise an LTSF SKU (list pending) | SEARCH TERM: buys 7 exact ranking terms (24 clicks, $83 in 30d) — “bamboo sheets” 15, “bamboo sheets queen size” 2, “bamboo sheets king size” 2, “king sheets bamboo” 2, “bamboo bed sheets” 1</t>
+          <t>SKU: Broad campaign advertises BAMBOO-KING-WHITE-6PCS; the King LTSF SKU is BAMBOO-KING-GREY-6PCS (32 sold in 30 days, 391 Available, 196 days) | SEARCH TERM: buys 7 exact ranking terms (24 clicks, $83 in 30d) — “bamboo sheets” 15, “bamboo sheets queen size” 2, “bamboo sheets king size” 2, “king sheets bamboo” 2, “bamboo bed sheets” 1</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
+          <t>advertise BAMBOO-KING-GREY-6PCS | negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
         </is>
       </c>
     </row>
@@ -40484,12 +40484,12 @@
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>SKU: Broad campaign advertises the White ranking SKU BAMBOO-QUEEN-WHITE-6PCS; it should advertise an LTSF SKU (list pending) | SEARCH TERM: buys 10 exact ranking terms (29 clicks, $78 in 30d) — “bamboo sheets” 12, “queen bamboo sheet set” 6, “bamboo sheets queen size” 3, “bamboo sheets queen” 2, “viscose bamboo sheets” 1</t>
+          <t>SKU: Broad campaign advertises BAMBOO-QUEEN-WHITE-6PCS; the Queen LTSF SKU is BAMBOO-QUEEN-LIGHTOLIVE-6PCS (11 sold in 30 days, 131 Available, 141 days) | SEARCH TERM: buys 10 exact ranking terms (29 clicks, $78 in 30d) — “bamboo sheets” 12, “queen bamboo sheet set” 6, “bamboo sheets queen size” 3, “bamboo sheets queen” 2, “viscose bamboo sheets” 1</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
+          <t>advertise BAMBOO-QUEEN-LIGHTOLIVE-6PCS | negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
         </is>
       </c>
     </row>
@@ -40600,10 +40600,14 @@
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>SKU: Auto campaign advertises the White ranking SKU BAMBOO-QUEEN-WHITE-6PCS; it should advertise an LTSF SKU (list pending)</t>
-        </is>
-      </c>
-      <c r="BA257" t="inlineStr"/>
+          <t>SKU: Auto campaign advertises BAMBOO-QUEEN-WHITE-6PCS; the Queen LTSF SKU is BAMBOO-QUEEN-LIGHTOLIVE-6PCS (11 sold in 30 days, 131 Available, 141 days)</t>
+        </is>
+      </c>
+      <c r="BA257" t="inlineStr">
+        <is>
+          <t>advertise BAMBOO-QUEEN-LIGHTOLIVE-6PCS</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -40712,12 +40716,12 @@
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>SKU: Broad campaign advertises the White ranking SKU BAMBOO-FULL-WHITE-6PCS; it should advertise an LTSF SKU (list pending) | SEARCH TERM: buys 6 exact ranking terms (13 clicks, $39 in 30d) — “bamboo sheets” 6, “queen bamboo sheet set” 2, “bamboo cooling sheets” 2, “bamboo sheets queen size” 1, “bamboo bed sheets” 1</t>
+          <t>SKU: Broad campaign advertises BAMBOO-FULL-WHITE-6PCS; the Full LTSF SKU is BAMBOO-FULL-OLIVE-6PCS (13 sold in 30 days, 259 Available, 480 days) | SEARCH TERM: buys 6 exact ranking terms (13 clicks, $39 in 30d) — “bamboo sheets” 6, “queen bamboo sheet set” 2, “bamboo cooling sheets” 2, “bamboo sheets queen size” 1, “bamboo bed sheets” 1</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
+          <t>advertise BAMBOO-FULL-OLIVE-6PCS | negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
         </is>
       </c>
     </row>
@@ -40828,12 +40832,12 @@
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>SKU: Broad campaign advertises the White ranking SKU BAMBOO-CALIFKING-WHITE-6PCS; it should advertise an LTSF SKU (list pending) | SEARCH TERM: buys 4 exact ranking terms (6 clicks, $15 in 30d) — “king bed bamboo sheets” 2, “bamboo cooling sheets king size” 2, “bamboo sheets” 1, “king bed sheets bamboo” 1</t>
+          <t>SKU: Broad campaign advertises BAMBOO-CALIFKING-WHITE-6PCS; the California King LTSF SKU is BAMBOO-CALIFKING-SAGE GREEN-6PCS (0 sold in 30 days, 27 Available, 338 days) | SEARCH TERM: buys 4 exact ranking terms (6 clicks, $15 in 30d) — “king bed bamboo sheets” 2, “bamboo cooling sheets king size” 2, “bamboo sheets” 1, “king bed sheets bamboo” 1</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
+          <t>advertise BAMBOO-CALIFKING-SAGE GREEN-6PCS | negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
         </is>
       </c>
     </row>
@@ -41056,12 +41060,12 @@
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>SKU: Broad campaign advertises the White ranking SKU BAMBOO-KING-WHITE-6PCS; it should advertise an LTSF SKU (list pending) | SEARCH TERM: buys 3 exact ranking terms (6 clicks, $19 in 30d) — “bamboo sheets king size” 4, “bamboo sheets king” 1, “bamboo cooling sheets king size” 1</t>
+          <t>SKU: Broad campaign advertises BAMBOO-KING-WHITE-6PCS; the King LTSF SKU is BAMBOO-KING-GREY-6PCS (32 sold in 30 days, 391 Available, 196 days) | SEARCH TERM: buys 3 exact ranking terms (6 clicks, $19 in 30d) — “bamboo sheets king size” 4, “bamboo sheets king” 1, “bamboo cooling sheets king size” 1</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
+          <t>advertise BAMBOO-KING-GREY-6PCS | negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
         </is>
       </c>
     </row>
@@ -41172,12 +41176,12 @@
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>SEARCH TERM: buys 1 exact ranking terms (1 clicks, $1 in 30d) — “bamboo sheets king size” 1</t>
+          <t>SKU: Auto campaign advertises BAMBOO-KING-TAUPE-6PCS; the King LTSF SKU is BAMBOO-KING-GREY-6PCS (32 sold in 30 days, 391 Available, 196 days) | SEARCH TERM: buys 1 exact ranking terms (1 clicks, $1 in 30d) — “bamboo sheets king size” 1</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
+          <t>advertise BAMBOO-KING-GREY-6PCS | negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
         </is>
       </c>
     </row>
@@ -41285,10 +41289,14 @@
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>SKU: Phrase campaign advertises the White ranking SKU BAMBOO-QUEEN-WHITE-6PCS; it should advertise an LTSF SKU (list pending)</t>
-        </is>
-      </c>
-      <c r="BA263" t="inlineStr"/>
+          <t>SKU: Phrase campaign advertises BAMBOO-QUEEN-WHITE-6PCS; the Queen LTSF SKU is BAMBOO-QUEEN-LIGHTOLIVE-6PCS (11 sold in 30 days, 131 Available, 141 days)</t>
+        </is>
+      </c>
+      <c r="BA263" t="inlineStr">
+        <is>
+          <t>advertise BAMBOO-QUEEN-LIGHTOLIVE-6PCS</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -41393,12 +41401,12 @@
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>SEARCH TERM: buys 2 exact ranking terms (2 clicks, $3 in 30d) — “bamboo sheets” 1, “bamboo sheets queen size” 1</t>
+          <t>SKU: Broad campaign advertises BAMBOO-QUEEN-BURGUNDY-6PCS; the Queen LTSF SKU is BAMBOO-QUEEN-LIGHTOLIVE-6PCS (11 sold in 30 days, 131 Available, 141 days) | SEARCH TERM: buys 2 exact ranking terms (2 clicks, $3 in 30d) — “bamboo sheets” 1, “bamboo sheets queen size” 1</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
+          <t>advertise BAMBOO-QUEEN-LIGHTOLIVE-6PCS | negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
         </is>
       </c>
     </row>
@@ -41505,10 +41513,14 @@
       <c r="AY265" t="inlineStr"/>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>SKU: Phrase campaign advertises the White ranking SKU BAMBOO-KING-WHITE-6PCS; it should advertise an LTSF SKU (list pending)</t>
-        </is>
-      </c>
-      <c r="BA265" t="inlineStr"/>
+          <t>SKU: Phrase campaign advertises BAMBOO-KING-WHITE-6PCS; the King LTSF SKU is BAMBOO-KING-GREY-6PCS (32 sold in 30 days, 391 Available, 196 days)</t>
+        </is>
+      </c>
+      <c r="BA265" t="inlineStr">
+        <is>
+          <t>advertise BAMBOO-KING-GREY-6PCS</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -41614,12 +41626,12 @@
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>SKU: Broad campaign advertises the White ranking SKU BAMBOO-QUEEN-WHITE-6PCS; it should advertise an LTSF SKU (list pending) | SEARCH TERM: buys 1 exact ranking terms (1 clicks, $1 in 30d) — “bamboo sheets” 1</t>
+          <t>SKU: Broad campaign advertises BAMBOO-QUEEN-WHITE-6PCS; the Queen LTSF SKU is BAMBOO-QUEEN-LIGHTOLIVE-6PCS (11 sold in 30 days, 131 Available, 141 days) | SEARCH TERM: buys 1 exact ranking terms (1 clicks, $1 in 30d) — “bamboo sheets” 1</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
+          <t>advertise BAMBOO-QUEEN-LIGHTOLIVE-6PCS | negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
         </is>
       </c>
     </row>
@@ -41721,8 +41733,16 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
-      <c r="AZ267" t="inlineStr"/>
-      <c r="BA267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>SKU: Auto campaign advertises BAMBOO-QUEEN-OLIVE-6PCS; the Queen LTSF SKU is BAMBOO-QUEEN-LIGHTOLIVE-6PCS (11 sold in 30 days, 131 Available, 141 days)</t>
+        </is>
+      </c>
+      <c r="BA267" t="inlineStr">
+        <is>
+          <t>advertise BAMBOO-QUEEN-LIGHTOLIVE-6PCS</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -41827,10 +41847,14 @@
       <c r="AY268" t="inlineStr"/>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>SKU: Broad campaign advertises the White ranking SKU BAMBOO-KING-WHITE-6PCS; it should advertise an LTSF SKU (list pending)</t>
-        </is>
-      </c>
-      <c r="BA268" t="inlineStr"/>
+          <t>SKU: Broad campaign advertises BAMBOO-KING-WHITE-6PCS; the King LTSF SKU is BAMBOO-KING-GREY-6PCS (32 sold in 30 days, 391 Available, 196 days)</t>
+        </is>
+      </c>
+      <c r="BA268" t="inlineStr">
+        <is>
+          <t>advertise BAMBOO-KING-GREY-6PCS</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -41936,10 +41960,14 @@
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>SKU: Auto campaign advertises the White ranking SKU BAMBOO-QUEEN-WHITE-6PCS; it should advertise an LTSF SKU (list pending)</t>
-        </is>
-      </c>
-      <c r="BA269" t="inlineStr"/>
+          <t>SKU: Auto campaign advertises BAMBOO-QUEEN-WHITE-6PCS; the Queen LTSF SKU is BAMBOO-QUEEN-LIGHTOLIVE-6PCS (11 sold in 30 days, 131 Available, 141 days)</t>
+        </is>
+      </c>
+      <c r="BA269" t="inlineStr">
+        <is>
+          <t>advertise BAMBOO-QUEEN-LIGHTOLIVE-6PCS</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -42039,8 +42067,16 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
-      <c r="AZ270" t="inlineStr"/>
-      <c r="BA270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>SKU: Auto campaign advertises BAMBOO-QUEEN-OLIVE-6PCS; the Queen LTSF SKU is BAMBOO-QUEEN-LIGHTOLIVE-6PCS (11 sold in 30 days, 131 Available, 141 days)</t>
+        </is>
+      </c>
+      <c r="BA270" t="inlineStr">
+        <is>
+          <t>advertise BAMBOO-QUEEN-LIGHTOLIVE-6PCS</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -42146,12 +42182,12 @@
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>SEARCH TERM: buys 1 exact ranking terms (1 clicks, $0 in 30d) — “bamboo sheets” 1</t>
+          <t>SKU: Auto campaign advertises BAMBOO-QUEEN-OLIVE-6PCS; the Queen LTSF SKU is BAMBOO-QUEEN-LIGHTOLIVE-6PCS (11 sold in 30 days, 131 Available, 141 days) | SEARCH TERM: buys 1 exact ranking terms (1 clicks, $0 in 30d) — “bamboo sheets” 1</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
+          <t>advertise BAMBOO-QUEEN-LIGHTOLIVE-6PCS | negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
         </is>
       </c>
     </row>
